--- a/network_overlap/Overlapping Gene from Network.xlsx
+++ b/network_overlap/Overlapping Gene from Network.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wgu/Desktop/CMSNetwork/network_overlap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0811A35D-9E45-A140-92EE-B49D1A46F7CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4533E25-A2B1-3E4C-A2AC-74079DA8F174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
